--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="325">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -545,7 +545,7 @@
 prior</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CommunicationRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/communicationrequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -738,7 +738,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -775,7 +775,7 @@
     <t>CommunicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -865,7 +865,17 @@
     <t>The communicated content (or for multi-part communications, one portion of the communication).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Request.note</t>
+  </si>
+  <si>
+    <t>CommunicationRequest.payload.content[x]:contentReference</t>
+  </si>
+  <si>
+    <t>contentReference</t>
   </si>
   <si>
     <t>CommunicationRequest.occurrence[x]</t>
@@ -921,7 +931,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -943,7 +953,7 @@
     <t>CommunicationRequest.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson|Group|CareTeam|HealthcareService) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -962,7 +972,7 @@
     <t>CommunicationRequest.sender</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson|HealthcareService) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1002,7 +1012,7 @@
     <t>CommunicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1330,12 +1340,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.8125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.1875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.33984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1343,7 +1353,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="148.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4554,16 +4564,14 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>266</v>
@@ -4581,7 +4589,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
@@ -4592,14 +4600,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4615,16 +4625,16 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4675,10 +4685,10 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>85</v>
@@ -4690,10 +4700,10 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -4701,14 +4711,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4727,13 +4737,13 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4784,7 +4794,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4799,10 +4809,10 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -4810,14 +4820,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4836,13 +4846,13 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4893,7 +4903,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4908,32 +4918,32 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -4942,16 +4952,16 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5002,13 +5012,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5017,21 +5027,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5042,7 +5052,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5051,16 +5061,16 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5111,13 +5121,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5126,10 +5136,10 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5137,10 +5147,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5151,7 +5161,7 @@
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5163,7 +5173,7 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>304</v>
@@ -5171,9 +5181,7 @@
       <c r="M35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5198,13 +5206,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5222,13 +5230,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5237,21 +5245,21 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5274,15 +5282,17 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5307,13 +5317,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5331,7 +5341,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5346,21 +5356,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5380,16 +5390,16 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5440,7 +5450,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5455,13 +5465,122 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s" s="2">
         <v>321</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-communicationrequest-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
